--- a/source/bin/excel/level_definition.xlsx
+++ b/source/bin/excel/level_definition.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Git\liqi-excel\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\quehun-cehua\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B92DAC0-A101-4E74-B5D9-2137DCEC051A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD9447EB-A7DF-419E-91BC-BC3B8466327D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="279">
   <si>
     <t>sheet</t>
   </si>
@@ -852,13 +852,25 @@
   </si>
   <si>
     <t>火数</t>
+  </si>
+  <si>
+    <t>30520013-1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>30550042-1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>30530013-1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -991,7 +1003,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1017,10 +1029,6 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1298,13 +1306,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.75" customWidth="1"/>
     <col min="2" max="2" width="11.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1318,7 +1326,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1329,7 +1337,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1343,7 +1351,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1357,7 +1365,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1381,7 +1389,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:X75"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.375" customWidth="1"/>
     <col min="2" max="2" width="6.375" customWidth="1"/>
@@ -1401,12 +1409,12 @@
     <col min="16" max="17" width="10.75" customWidth="1"/>
     <col min="18" max="18" width="9.375" customWidth="1"/>
     <col min="19" max="21" width="12.375" customWidth="1"/>
-    <col min="22" max="22" width="14.125" style="16" customWidth="1"/>
-    <col min="23" max="23" width="15.125" style="16" customWidth="1"/>
+    <col min="22" max="22" width="14.125" customWidth="1"/>
+    <col min="23" max="23" width="15.125" customWidth="1"/>
     <col min="24" max="24" width="22.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="15" customHeight="1">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -1470,33 +1478,33 @@
       <c r="U1" t="s">
         <v>33</v>
       </c>
-      <c r="V1" s="16" t="s">
+      <c r="V1" t="s">
         <v>34</v>
       </c>
-      <c r="W1" s="16" t="s">
+      <c r="W1" t="s">
         <v>35</v>
       </c>
       <c r="X1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" ht="15" customHeight="1">
       <c r="A2" t="s">
         <v>37</v>
       </c>
       <c r="M2" s="10"/>
       <c r="R2" s="10"/>
-      <c r="V2" s="16" t="s">
+      <c r="V2" t="s">
         <v>38</v>
       </c>
-      <c r="W2" s="16" t="s">
+      <c r="W2" t="s">
         <v>39</v>
       </c>
       <c r="X2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="15" customHeight="1">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1560,17 +1568,17 @@
       <c r="U3" t="s">
         <v>42</v>
       </c>
-      <c r="V3" s="16" t="s">
+      <c r="V3" t="s">
         <v>43</v>
       </c>
-      <c r="W3" s="16" t="s">
+      <c r="W3" t="s">
         <v>43</v>
       </c>
       <c r="X3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24">
       <c r="B4">
         <v>10101</v>
       </c>
@@ -1631,14 +1639,14 @@
       <c r="U4">
         <v>1</v>
       </c>
-      <c r="V4" s="17">
+      <c r="V4" s="2">
         <v>0</v>
       </c>
-      <c r="W4" s="17">
+      <c r="W4" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24">
       <c r="B5">
         <v>10102</v>
       </c>
@@ -1699,14 +1707,14 @@
       <c r="U5">
         <v>1</v>
       </c>
-      <c r="V5" s="17">
+      <c r="V5" s="2">
         <v>0</v>
       </c>
-      <c r="W5" s="17">
+      <c r="W5" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24">
       <c r="B6">
         <v>10103</v>
       </c>
@@ -1767,14 +1775,14 @@
       <c r="U6">
         <v>1</v>
       </c>
-      <c r="V6" s="17">
+      <c r="V6" s="2">
         <v>0</v>
       </c>
-      <c r="W6" s="17">
+      <c r="W6" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" ht="15" customHeight="1">
       <c r="B7">
         <v>10201</v>
       </c>
@@ -1835,14 +1843,14 @@
       <c r="U7">
         <v>1</v>
       </c>
-      <c r="V7" s="17">
+      <c r="V7" s="2">
         <v>-10</v>
       </c>
-      <c r="W7" s="17">
+      <c r="W7" s="2">
         <v>-20</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" ht="15" customHeight="1">
       <c r="B8">
         <v>10202</v>
       </c>
@@ -1903,14 +1911,14 @@
       <c r="U8">
         <v>1</v>
       </c>
-      <c r="V8" s="17">
+      <c r="V8" s="2">
         <v>-20</v>
       </c>
-      <c r="W8" s="17">
+      <c r="W8" s="2">
         <v>-40</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" ht="15" customHeight="1">
       <c r="B9">
         <v>10203</v>
       </c>
@@ -1971,14 +1979,14 @@
       <c r="U9">
         <v>1</v>
       </c>
-      <c r="V9" s="17">
+      <c r="V9" s="2">
         <v>-30</v>
       </c>
-      <c r="W9" s="17">
+      <c r="W9" s="2">
         <v>-60</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" ht="15" customHeight="1">
       <c r="B10">
         <v>10301</v>
       </c>
@@ -2039,14 +2047,14 @@
       <c r="U10">
         <v>1</v>
       </c>
-      <c r="V10" s="17">
+      <c r="V10" s="2">
         <v>-40</v>
       </c>
-      <c r="W10" s="17">
+      <c r="W10" s="2">
         <v>-80</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" ht="15" customHeight="1">
       <c r="B11">
         <v>10302</v>
       </c>
@@ -2107,14 +2115,14 @@
       <c r="U11">
         <v>1</v>
       </c>
-      <c r="V11" s="17">
+      <c r="V11" s="2">
         <v>-50</v>
       </c>
-      <c r="W11" s="17">
+      <c r="W11" s="2">
         <v>-100</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" ht="15" customHeight="1">
       <c r="B12">
         <v>10303</v>
       </c>
@@ -2175,14 +2183,14 @@
       <c r="U12">
         <v>1</v>
       </c>
-      <c r="V12" s="17">
+      <c r="V12" s="2">
         <v>-60</v>
       </c>
-      <c r="W12" s="17">
+      <c r="W12" s="2">
         <v>-120</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" ht="15" customHeight="1">
       <c r="B13">
         <v>10401</v>
       </c>
@@ -2243,14 +2251,14 @@
       <c r="U13">
         <v>1</v>
       </c>
-      <c r="V13" s="17">
+      <c r="V13" s="2">
         <v>-80</v>
       </c>
-      <c r="W13" s="17">
+      <c r="W13" s="2">
         <v>-165</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" ht="15" customHeight="1">
       <c r="B14">
         <v>10402</v>
       </c>
@@ -2311,14 +2319,14 @@
       <c r="U14">
         <v>1</v>
       </c>
-      <c r="V14" s="17">
+      <c r="V14" s="2">
         <v>-90</v>
       </c>
-      <c r="W14" s="17">
+      <c r="W14" s="2">
         <v>-180</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" ht="15" customHeight="1">
       <c r="B15">
         <v>10403</v>
       </c>
@@ -2379,14 +2387,14 @@
       <c r="U15">
         <v>1</v>
       </c>
-      <c r="V15" s="17">
+      <c r="V15" s="2">
         <v>-100</v>
       </c>
-      <c r="W15" s="17">
+      <c r="W15" s="2">
         <v>-195</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" ht="15" customHeight="1">
       <c r="B16">
         <v>10501</v>
       </c>
@@ -2447,14 +2455,14 @@
       <c r="U16">
         <v>1</v>
       </c>
-      <c r="V16" s="17">
+      <c r="V16" s="2">
         <v>-110</v>
       </c>
-      <c r="W16" s="17">
+      <c r="W16" s="2">
         <v>-210</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:24" ht="15" customHeight="1">
       <c r="B17">
         <v>10502</v>
       </c>
@@ -2515,14 +2523,14 @@
       <c r="U17">
         <v>1</v>
       </c>
-      <c r="V17" s="17">
+      <c r="V17" s="2">
         <v>-120</v>
       </c>
-      <c r="W17" s="17">
+      <c r="W17" s="2">
         <v>-225</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:24" ht="15" customHeight="1">
       <c r="B18">
         <v>10503</v>
       </c>
@@ -2583,14 +2591,14 @@
       <c r="U18">
         <v>1</v>
       </c>
-      <c r="V18" s="17">
+      <c r="V18" s="2">
         <v>-130</v>
       </c>
-      <c r="W18" s="17">
+      <c r="W18" s="2">
         <v>-240</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:24">
       <c r="B19">
         <v>10601</v>
       </c>
@@ -2651,14 +2659,14 @@
       <c r="U19">
         <v>1</v>
       </c>
-      <c r="V19" s="17">
+      <c r="V19" s="2">
         <v>-140</v>
       </c>
-      <c r="W19" s="16">
+      <c r="W19">
         <v>-255</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:24">
       <c r="A20" t="s">
         <v>137</v>
       </c>
@@ -2726,7 +2734,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:24">
       <c r="A21" t="s">
         <v>140</v>
       </c>
@@ -2794,7 +2802,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:24">
       <c r="A22" t="s">
         <v>143</v>
       </c>
@@ -2862,7 +2870,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:24">
       <c r="A23" t="s">
         <v>146</v>
       </c>
@@ -2930,7 +2938,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:24">
       <c r="A24" t="s">
         <v>149</v>
       </c>
@@ -2998,7 +3006,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:24">
       <c r="A25" t="s">
         <v>152</v>
       </c>
@@ -3066,7 +3074,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:24">
       <c r="A26" t="s">
         <v>155</v>
       </c>
@@ -3134,7 +3142,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:24">
       <c r="A27" t="s">
         <v>158</v>
       </c>
@@ -3202,7 +3210,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:24">
       <c r="A28" t="s">
         <v>161</v>
       </c>
@@ -3270,7 +3278,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:24">
       <c r="A29" t="s">
         <v>164</v>
       </c>
@@ -3338,7 +3346,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:24">
       <c r="A30" t="s">
         <v>167</v>
       </c>
@@ -3406,7 +3414,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:24">
       <c r="A31" t="s">
         <v>170</v>
       </c>
@@ -3474,7 +3482,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:24">
       <c r="A32" t="s">
         <v>173</v>
       </c>
@@ -3542,7 +3550,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:24">
       <c r="A33" t="s">
         <v>176</v>
       </c>
@@ -3610,7 +3618,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:24">
       <c r="A34" t="s">
         <v>179</v>
       </c>
@@ -3678,7 +3686,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:24">
       <c r="A35" t="s">
         <v>182</v>
       </c>
@@ -3746,7 +3754,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:24">
       <c r="A36" t="s">
         <v>185</v>
       </c>
@@ -3814,7 +3822,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:24">
       <c r="A37" t="s">
         <v>188</v>
       </c>
@@ -3882,7 +3890,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:24">
       <c r="A38" t="s">
         <v>191</v>
       </c>
@@ -3950,7 +3958,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:24">
       <c r="A39" t="s">
         <v>194</v>
       </c>
@@ -4018,7 +4026,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:24">
       <c r="B40">
         <v>20101</v>
       </c>
@@ -4079,14 +4087,14 @@
       <c r="U40">
         <v>1</v>
       </c>
-      <c r="V40" s="17">
+      <c r="V40" s="2">
         <v>0</v>
       </c>
-      <c r="W40" s="17">
+      <c r="W40" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:24">
       <c r="B41">
         <v>20102</v>
       </c>
@@ -4147,14 +4155,14 @@
       <c r="U41">
         <v>1</v>
       </c>
-      <c r="V41" s="17">
+      <c r="V41" s="2">
         <v>0</v>
       </c>
-      <c r="W41" s="17">
+      <c r="W41" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:24">
       <c r="B42">
         <v>20103</v>
       </c>
@@ -4215,14 +4223,14 @@
       <c r="U42">
         <v>1</v>
       </c>
-      <c r="V42" s="17">
+      <c r="V42" s="2">
         <v>0</v>
       </c>
-      <c r="W42" s="17">
+      <c r="W42" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:24" ht="15" customHeight="1">
       <c r="B43">
         <v>20201</v>
       </c>
@@ -4283,14 +4291,14 @@
       <c r="U43">
         <v>1</v>
       </c>
-      <c r="V43" s="17">
+      <c r="V43" s="2">
         <v>-10</v>
       </c>
-      <c r="W43" s="17">
+      <c r="W43" s="2">
         <v>-20</v>
       </c>
     </row>
-    <row r="44" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:24" ht="15" customHeight="1">
       <c r="B44">
         <v>20202</v>
       </c>
@@ -4351,14 +4359,14 @@
       <c r="U44">
         <v>1</v>
       </c>
-      <c r="V44" s="17">
+      <c r="V44" s="2">
         <v>-20</v>
       </c>
-      <c r="W44" s="17">
+      <c r="W44" s="2">
         <v>-40</v>
       </c>
     </row>
-    <row r="45" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:24" ht="15" customHeight="1">
       <c r="B45">
         <v>20203</v>
       </c>
@@ -4419,14 +4427,14 @@
       <c r="U45">
         <v>1</v>
       </c>
-      <c r="V45" s="17">
+      <c r="V45" s="2">
         <v>-30</v>
       </c>
-      <c r="W45" s="17">
+      <c r="W45" s="2">
         <v>-60</v>
       </c>
     </row>
-    <row r="46" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:24" ht="15" customHeight="1">
       <c r="B46">
         <v>20301</v>
       </c>
@@ -4487,14 +4495,14 @@
       <c r="U46">
         <v>1</v>
       </c>
-      <c r="V46" s="17">
+      <c r="V46" s="2">
         <v>-40</v>
       </c>
-      <c r="W46" s="17">
+      <c r="W46" s="2">
         <v>-80</v>
       </c>
     </row>
-    <row r="47" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:24" ht="15" customHeight="1">
       <c r="B47">
         <v>20302</v>
       </c>
@@ -4555,14 +4563,14 @@
       <c r="U47">
         <v>1</v>
       </c>
-      <c r="V47" s="17">
+      <c r="V47" s="2">
         <v>-50</v>
       </c>
-      <c r="W47" s="17">
+      <c r="W47" s="2">
         <v>-100</v>
       </c>
     </row>
-    <row r="48" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:24" ht="15" customHeight="1">
       <c r="B48">
         <v>20303</v>
       </c>
@@ -4623,14 +4631,14 @@
       <c r="U48">
         <v>1</v>
       </c>
-      <c r="V48" s="17">
+      <c r="V48" s="2">
         <v>-60</v>
       </c>
-      <c r="W48" s="17">
+      <c r="W48" s="2">
         <v>-120</v>
       </c>
     </row>
-    <row r="49" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:24" ht="15" customHeight="1">
       <c r="B49">
         <v>20401</v>
       </c>
@@ -4691,14 +4699,14 @@
       <c r="U49">
         <v>1</v>
       </c>
-      <c r="V49" s="17">
+      <c r="V49" s="2">
         <v>-80</v>
       </c>
-      <c r="W49" s="17">
+      <c r="W49" s="2">
         <v>-165</v>
       </c>
     </row>
-    <row r="50" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:24" ht="15" customHeight="1">
       <c r="B50">
         <v>20402</v>
       </c>
@@ -4759,14 +4767,14 @@
       <c r="U50">
         <v>1</v>
       </c>
-      <c r="V50" s="17">
+      <c r="V50" s="2">
         <v>-95</v>
       </c>
-      <c r="W50" s="17">
+      <c r="W50" s="2">
         <v>-190</v>
       </c>
     </row>
-    <row r="51" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:24" ht="15" customHeight="1">
       <c r="B51">
         <v>20403</v>
       </c>
@@ -4827,14 +4835,14 @@
       <c r="U51">
         <v>1</v>
       </c>
-      <c r="V51" s="17">
+      <c r="V51" s="2">
         <v>-110</v>
       </c>
-      <c r="W51" s="17">
+      <c r="W51" s="2">
         <v>-215</v>
       </c>
     </row>
-    <row r="52" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:24" ht="15" customHeight="1">
       <c r="B52">
         <v>20501</v>
       </c>
@@ -4895,14 +4903,14 @@
       <c r="U52">
         <v>1</v>
       </c>
-      <c r="V52" s="17">
+      <c r="V52" s="2">
         <v>-125</v>
       </c>
-      <c r="W52" s="17">
+      <c r="W52" s="2">
         <v>-240</v>
       </c>
     </row>
-    <row r="53" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:24" ht="15" customHeight="1">
       <c r="B53">
         <v>20502</v>
       </c>
@@ -4963,14 +4971,14 @@
       <c r="U53">
         <v>1</v>
       </c>
-      <c r="V53" s="17">
+      <c r="V53" s="2">
         <v>-140</v>
       </c>
-      <c r="W53" s="17">
+      <c r="W53" s="2">
         <v>-265</v>
       </c>
     </row>
-    <row r="54" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:24" ht="15" customHeight="1">
       <c r="B54">
         <v>20503</v>
       </c>
@@ -5031,14 +5039,14 @@
       <c r="U54">
         <v>1</v>
       </c>
-      <c r="V54" s="17">
+      <c r="V54" s="2">
         <v>-160</v>
       </c>
-      <c r="W54" s="17">
+      <c r="W54" s="2">
         <v>-290</v>
       </c>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:24">
       <c r="B55">
         <v>20601</v>
       </c>
@@ -5099,14 +5107,14 @@
       <c r="U55">
         <v>1</v>
       </c>
-      <c r="V55" s="17">
+      <c r="V55" s="2">
         <v>-175</v>
       </c>
-      <c r="W55" s="16">
+      <c r="W55">
         <v>-320</v>
       </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:24">
       <c r="A56" t="s">
         <v>137</v>
       </c>
@@ -5174,7 +5182,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:24">
       <c r="A57" t="s">
         <v>140</v>
       </c>
@@ -5242,7 +5250,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:24">
       <c r="A58" t="s">
         <v>143</v>
       </c>
@@ -5310,7 +5318,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:24">
       <c r="A59" t="s">
         <v>146</v>
       </c>
@@ -5378,7 +5386,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:24">
       <c r="A60" t="s">
         <v>149</v>
       </c>
@@ -5446,7 +5454,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:24">
       <c r="A61" t="s">
         <v>152</v>
       </c>
@@ -5514,7 +5522,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:24">
       <c r="A62" t="s">
         <v>155</v>
       </c>
@@ -5582,7 +5590,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:24">
       <c r="A63" t="s">
         <v>158</v>
       </c>
@@ -5650,7 +5658,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:24">
       <c r="A64" t="s">
         <v>161</v>
       </c>
@@ -5718,7 +5726,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:24">
       <c r="A65" t="s">
         <v>164</v>
       </c>
@@ -5786,7 +5794,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="66" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:24">
       <c r="A66" t="s">
         <v>167</v>
       </c>
@@ -5854,7 +5862,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="67" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:24">
       <c r="A67" t="s">
         <v>170</v>
       </c>
@@ -5922,7 +5930,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="68" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:24">
       <c r="A68" t="s">
         <v>173</v>
       </c>
@@ -5990,7 +5998,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="69" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:24">
       <c r="A69" t="s">
         <v>176</v>
       </c>
@@ -6058,7 +6066,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="70" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:24">
       <c r="A70" t="s">
         <v>179</v>
       </c>
@@ -6126,7 +6134,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="71" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:24">
       <c r="A71" t="s">
         <v>182</v>
       </c>
@@ -6194,7 +6202,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="72" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:24">
       <c r="A72" t="s">
         <v>185</v>
       </c>
@@ -6262,7 +6270,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="73" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:24">
       <c r="A73" t="s">
         <v>188</v>
       </c>
@@ -6330,7 +6338,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="74" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:24">
       <c r="A74" t="s">
         <v>191</v>
       </c>
@@ -6398,7 +6406,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="75" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:24">
       <c r="A75" t="s">
         <v>194</v>
       </c>
@@ -6476,14 +6484,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="17.875" customWidth="1"/>
     <col min="3" max="6" width="14.125" customWidth="1"/>
     <col min="7" max="10" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -6518,7 +6526,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -6547,7 +6555,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -6582,7 +6590,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11">
       <c r="B4">
         <v>1001</v>
       </c>
@@ -6614,7 +6622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11">
       <c r="B5">
         <v>1001</v>
       </c>
@@ -6646,7 +6654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11">
       <c r="B6">
         <v>1001</v>
       </c>
@@ -6672,7 +6680,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11">
       <c r="B7">
         <v>1001</v>
       </c>
@@ -6707,8 +6715,8 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:K33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:K38"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="3" max="3" width="11.875" customWidth="1"/>
     <col min="5" max="5" width="24.625" customWidth="1"/>
@@ -6720,7 +6728,7 @@
     <col min="11" max="11" width="61.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="15" customHeight="1">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -6755,7 +6763,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="15" customHeight="1">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -6773,7 +6781,7 @@
       </c>
       <c r="K2" s="10"/>
     </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15" customHeight="1">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -6808,7 +6816,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="16.5" customHeight="1">
       <c r="B4">
         <v>1</v>
       </c>
@@ -6834,7 +6842,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="33" customHeight="1">
       <c r="B5">
         <v>2</v>
       </c>
@@ -6860,7 +6868,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="33" customHeight="1">
       <c r="B6">
         <v>3</v>
       </c>
@@ -6886,7 +6894,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11">
       <c r="B7">
         <v>4</v>
       </c>
@@ -6912,7 +6920,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="28.5" customHeight="1">
       <c r="B8">
         <v>5</v>
       </c>
@@ -6938,7 +6946,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="16.5" customHeight="1">
       <c r="B9">
         <v>1</v>
       </c>
@@ -6964,7 +6972,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="33" customHeight="1">
       <c r="B10">
         <v>2</v>
       </c>
@@ -6993,7 +7001,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="33" customHeight="1">
       <c r="B11">
         <v>3</v>
       </c>
@@ -7022,7 +7030,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11">
       <c r="B12">
         <v>4</v>
       </c>
@@ -7051,7 +7059,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="28.5" customHeight="1">
       <c r="B13">
         <v>5</v>
       </c>
@@ -7077,7 +7085,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="16.5" customHeight="1">
       <c r="B14">
         <v>1</v>
       </c>
@@ -7103,7 +7111,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="33" customHeight="1">
       <c r="B15">
         <v>2</v>
       </c>
@@ -7132,7 +7140,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="33" customHeight="1">
       <c r="B16">
         <v>3</v>
       </c>
@@ -7161,7 +7169,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:11">
       <c r="B17">
         <v>4</v>
       </c>
@@ -7190,7 +7198,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="18" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:11" ht="28.5" customHeight="1">
       <c r="B18">
         <v>5</v>
       </c>
@@ -7216,7 +7224,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="19" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:11" ht="16.5" customHeight="1">
       <c r="B19">
         <v>1</v>
       </c>
@@ -7242,7 +7250,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="20" spans="2:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:11" ht="33" customHeight="1">
       <c r="B20">
         <v>2</v>
       </c>
@@ -7271,7 +7279,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="21" spans="2:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:11" ht="33" customHeight="1">
       <c r="B21">
         <v>3</v>
       </c>
@@ -7300,7 +7308,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:11">
       <c r="B22">
         <v>4</v>
       </c>
@@ -7329,7 +7337,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="23" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:11" ht="28.5" customHeight="1">
       <c r="B23">
         <v>5</v>
       </c>
@@ -7355,7 +7363,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="24" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:11" ht="16.5" customHeight="1">
       <c r="B24">
         <v>1</v>
       </c>
@@ -7381,7 +7389,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="25" spans="2:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:11" ht="33" customHeight="1">
       <c r="B25">
         <v>2</v>
       </c>
@@ -7410,7 +7418,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:11" ht="33" customHeight="1">
       <c r="B26">
         <v>3</v>
       </c>
@@ -7439,7 +7447,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:11">
       <c r="B27">
         <v>4</v>
       </c>
@@ -7468,7 +7476,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="28" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:11" ht="28.5" customHeight="1">
       <c r="B28">
         <v>5</v>
       </c>
@@ -7494,7 +7502,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="29" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:11" ht="16.5" customHeight="1">
       <c r="B29">
         <v>1</v>
       </c>
@@ -7520,7 +7528,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="30" spans="2:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:11" ht="33" customHeight="1">
       <c r="B30">
         <v>2</v>
       </c>
@@ -7549,7 +7557,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="31" spans="2:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:11" ht="33" customHeight="1">
       <c r="B31">
         <v>3</v>
       </c>
@@ -7578,7 +7586,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:11">
       <c r="B32">
         <v>4</v>
       </c>
@@ -7607,7 +7615,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="33" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:11" ht="28.5" customHeight="1">
       <c r="B33">
         <v>5</v>
       </c>
@@ -7630,6 +7638,145 @@
         <v>251</v>
       </c>
       <c r="K33" s="12" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" ht="16.5" customHeight="1">
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34">
+        <v>20000121</v>
+      </c>
+      <c r="D34">
+        <v>2000</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="K34" s="15" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" ht="33" customHeight="1">
+      <c r="B35">
+        <v>2</v>
+      </c>
+      <c r="C35">
+        <v>20000121</v>
+      </c>
+      <c r="D35">
+        <v>6000</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="K35" s="15" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" ht="33" customHeight="1">
+      <c r="B36">
+        <v>3</v>
+      </c>
+      <c r="C36">
+        <v>20000121</v>
+      </c>
+      <c r="D36">
+        <v>10000</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="K36" s="15" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11">
+      <c r="B37">
+        <v>4</v>
+      </c>
+      <c r="C37">
+        <v>20000121</v>
+      </c>
+      <c r="D37">
+        <v>20000</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="G37" t="s">
+        <v>243</v>
+      </c>
+      <c r="H37" t="s">
+        <v>244</v>
+      </c>
+      <c r="I37" t="s">
+        <v>245</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="K37" s="12" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" ht="28.5" customHeight="1">
+      <c r="B38">
+        <v>5</v>
+      </c>
+      <c r="C38">
+        <v>20000121</v>
+      </c>
+      <c r="D38">
+        <v>50000</v>
+      </c>
+      <c r="G38" t="s">
+        <v>248</v>
+      </c>
+      <c r="H38" t="s">
+        <v>249</v>
+      </c>
+      <c r="I38" t="s">
+        <v>250</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="K38" s="12" t="s">
         <v>252</v>
       </c>
     </row>
@@ -7643,7 +7790,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.375" customWidth="1"/>
     <col min="2" max="2" width="6.375" customWidth="1"/>
@@ -7652,7 +7799,7 @@
     <col min="6" max="6" width="7.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -7672,7 +7819,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -7689,7 +7836,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -7709,7 +7856,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6">
       <c r="B4">
         <v>1</v>
       </c>
@@ -7726,7 +7873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6">
       <c r="B5">
         <v>2</v>
       </c>
@@ -7743,7 +7890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6">
       <c r="B6">
         <v>3</v>
       </c>
@@ -7760,7 +7907,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6">
       <c r="B7">
         <v>4</v>
       </c>
@@ -7777,7 +7924,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6">
       <c r="B8">
         <v>5</v>
       </c>
@@ -7794,7 +7941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6">
       <c r="B9">
         <v>6</v>
       </c>
@@ -7811,7 +7958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6">
       <c r="B10">
         <v>7</v>
       </c>
@@ -7828,7 +7975,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6">
       <c r="B11">
         <v>8</v>
       </c>
@@ -7845,7 +7992,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6">
       <c r="B12">
         <v>9</v>
       </c>
@@ -7862,7 +8009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6">
       <c r="B13">
         <v>10</v>
       </c>
@@ -7879,7 +8026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6">
       <c r="B14">
         <v>11</v>
       </c>
@@ -7896,7 +8043,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6">
       <c r="B15">
         <v>12</v>
       </c>
@@ -7913,7 +8060,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6">
       <c r="B16">
         <v>13</v>
       </c>
